--- a/results/Int All Data -0.0/Rando_10_permute.xlsx
+++ b/results/Int All Data -0.0/Rando_10_permute.xlsx
@@ -440,1543 +440,1543 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8555977635229293</v>
+        <v>0.850297565458854</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8552801015153053</v>
+        <v>0.848473515650134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8562149537096693</v>
+        <v>0.8445165009305855</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8562149537096693</v>
+        <v>0.849335832530467</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8569409468674558</v>
+        <v>0.8495171708155445</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8573130103606029</v>
+        <v>0.8507696850175321</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8569772145244713</v>
+        <v>0.8504701568384161</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8475386634557701</v>
+        <v>0.849163241150905</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8417482120045091</v>
+        <v>0.849163241150905</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8404050286599827</v>
+        <v>0.8481739874710179</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8441531843429538</v>
+        <v>0.8505064244954316</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8460591563886971</v>
+        <v>0.8498892343086916</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8408496274671606</v>
+        <v>0.8498892343086916</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8404956978025213</v>
+        <v>0.8498892343086916</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8431820644915744</v>
+        <v>0.8498892343086916</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8431820644915744</v>
+        <v>0.8546991789855809</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.841593754453455</v>
+        <v>0.8467401349839526</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8410759803147692</v>
+        <v>0.8481195859854946</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8419926986806253</v>
+        <v>0.8446246638841551</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8454507131074726</v>
+        <v>0.844942325891779</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8454507131074726</v>
+        <v>0.8442888680480235</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8435628748902371</v>
+        <v>0.8432176921311132</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8417838396440479</v>
+        <v>0.8413842553994008</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8427368256669195</v>
+        <v>0.8333339022377571</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8317280983886066</v>
+        <v>0.8362109941348799</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8357126338596552</v>
+        <v>0.8344050781546675</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8341243238215358</v>
+        <v>0.8298214863253865</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8258651116233147</v>
+        <v>0.8254104858756677</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8274534216614342</v>
+        <v>0.828550838294891</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8271176258253026</v>
+        <v>0.8282519501332517</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8242768015851953</v>
+        <v>0.825012181665974</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8266092386096089</v>
+        <v>0.8256475056812218</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8253016829046211</v>
+        <v>0.8263190973534851</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8255924641782219</v>
+        <v>0.8259833015173534</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8223520556934675</v>
+        <v>0.8237684143695017</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8198382803839763</v>
+        <v>0.8205642735417629</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8215441402986577</v>
+        <v>0.8219887391058358</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8215441402986577</v>
+        <v>0.8198013727094842</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8208725486263946</v>
+        <v>0.8185851261645118</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8202553584396544</v>
+        <v>0.8197013166439532</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8180135905577794</v>
+        <v>0.8222970141904675</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8160626039495051</v>
+        <v>0.8220337536683668</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8164346674426524</v>
+        <v>0.8223695495044985</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8161170054350284</v>
+        <v>0.8226872115121223</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8145374423024244</v>
+        <v>0.8192010363162984</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8162433022171058</v>
+        <v>0.8169505215289079</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8183850140334499</v>
+        <v>0.8217879869572973</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8190566057057131</v>
+        <v>0.819491817589899</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8143098094198626</v>
+        <v>0.7979439225220444</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8161795138085904</v>
+        <v>0.8084086349451249</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8168329716523459</v>
+        <v>0.8038525638673439</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8153353307567652</v>
+        <v>0.7772771181805072</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8117228587788636</v>
+        <v>0.7733926387749894</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8117228587788636</v>
+        <v>0.7730837236728811</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8117228587788636</v>
+        <v>0.7670206247765272</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8088276330532332</v>
+        <v>0.7670206247765272</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8084193019030707</v>
+        <v>0.7777942523017162</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8017846673999844</v>
+        <v>0.77811191430934</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8019116041995387</v>
+        <v>0.7395384876643032</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7991977167589857</v>
+        <v>0.7366069942816572</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7911017090173342</v>
+        <v>0.7462913120614281</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7878975681895954</v>
+        <v>0.7469629037336913</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7903844627650632</v>
+        <v>0.7426244385980033</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7948317308717976</v>
+        <v>0.744884340308386</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7696813907665105</v>
+        <v>0.7487144182283805</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7901037084319316</v>
+        <v>0.7491233893960199</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7877712714075179</v>
+        <v>0.7473987556353539</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7865456379395533</v>
+        <v>0.7473987556353539</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7852481091750345</v>
+        <v>0.74831547400121</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7852481091750345</v>
+        <v>0.7530528833640684</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7657612837214542</v>
+        <v>0.7314606137511594</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7615047408227894</v>
+        <v>0.7345009101048519</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7628116565103005</v>
+        <v>0.7328044371131628</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7559950437046601</v>
+        <v>0.7328044371131628</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7559950437046601</v>
+        <v>0.7246540278859881</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7551602475758271</v>
+        <v>0.7252530842442204</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7526370853433437</v>
+        <v>0.7248810207510733</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7526370853433437</v>
+        <v>0.7196077034210214</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7454490490620331</v>
+        <v>0.720878351451517</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.744831858875293</v>
+        <v>0.7205606894438932</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7464927042274434</v>
+        <v>0.7205606894438932</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7426263586504336</v>
+        <v>0.7120926182090945</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7375800341854668</v>
+        <v>0.7108313571015912</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7205532225733311</v>
+        <v>0.7215230623897571</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7196183703789671</v>
+        <v>0.7131093926404817</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7160058984010657</v>
+        <v>0.7035338778317572</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7163235604086895</v>
+        <v>0.7005586499215339</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7190918493347658</v>
+        <v>0.6612935777232958</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7235766651334692</v>
+        <v>0.655312401063965</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7241938553202092</v>
+        <v>0.6510646050708158</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7396504907227334</v>
+        <v>0.6465085339930349</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7169226167669218</v>
+        <v>0.6435676536873967</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7039978905023967</v>
+        <v>0.6442211115311522</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7039978905023967</v>
+        <v>0.6391922808772165</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7039978905023967</v>
+        <v>0.6068626513961342</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7045975868781057</v>
+        <v>0.6081514332551374</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7053961153499232</v>
+        <v>0.6081514332551374</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6822518033559103</v>
+        <v>0.62134006005924</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.682342472498449</v>
+        <v>0.6208498066720541</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6751181685601229</v>
+        <v>0.6284562010439965</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6668139417993707</v>
+        <v>0.6062192204928476</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.655324988074341</v>
+        <v>0.6091963684555013</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6578938048868321</v>
+        <v>0.6087242488968232</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6569226850354527</v>
+        <v>0.5902904655316454</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6401497470224253</v>
+        <v>0.5893374795087738</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6274345198119543</v>
+        <v>0.5893374795087738</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5484843106115751</v>
+        <v>0.5884207611429176</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5463244649667234</v>
+        <v>0.5869231202473368</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5459867490781616</v>
+        <v>0.5403074473286951</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5526207435637709</v>
+        <v>0.5400079191495789</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5688127590470737</v>
+        <v>0.5346983341625116</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5640753496842155</v>
+        <v>0.5337816157966554</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5344783814896705</v>
+        <v>0.5340992778042792</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5389143426209825</v>
+        <v>0.5117266135480606</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5241924472817605</v>
+        <v>0.5117266135480606</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5338586312330236</v>
+        <v>0.5117447473765684</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5279231091537006</v>
+        <v>0.5066984229116016</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5138196840361721</v>
+        <v>0.5029771479626537</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5122495078265603</v>
+        <v>0.5026776197835375</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5168574203199575</v>
+        <v>0.5026594859550298</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5181912167414918</v>
+        <v>0.5026594859550298</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5187190178206467</v>
+        <v>0.5014976408955807</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5244362939403999</v>
+        <v>0.5030859509337001</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5253348784777483</v>
+        <v>0.502786422754584</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5199258774426267</v>
+        <v>0.5024687607469601</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3969164384648797</v>
+        <v>0.5024687607469601</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.3884846348870967</v>
+        <v>0.5021510987393363</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.3999354009026806</v>
+        <v>0.5021510987393363</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.3969851336740502</v>
+        <v>0.5021510987393363</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.3998891063051961</v>
+        <v>0.5021510987393363</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.3998891063051961</v>
+        <v>0.5015157747240885</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.3998891063051961</v>
+        <v>0.5012162465449723</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.3977380075658599</v>
+        <v>0.5015883100381194</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4304008728131669</v>
+        <v>0.5012706480304956</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4337225635174678</v>
+        <v>0.5022055002248594</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4390590292385584</v>
+        <v>0.5002813943506084</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4273336957254513</v>
+        <v>0.50061719018674</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4222423566979536</v>
+        <v>0.5002995281791162</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4220972860698916</v>
+        <v>0.5002995281791162</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4271342236118661</v>
+        <v>0.5002995281791162</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4192839825812844</v>
+        <v>0.5002995281791162</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4192839825812844</v>
+        <v>0.5002995281791162</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4649965908402406</v>
+        <v>0.5003176620076238</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4635446045246675</v>
+        <v>0.5006353240152478</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4334955706523826</v>
+        <v>0.5006353240152478</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4969234359892921</v>
+        <v>0.5006353240152478</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4932296817918441</v>
+        <v>0.5006353240152478</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4932296817918441</v>
+        <v>0.5006353240152478</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4968871683322766</v>
+        <v>0.5003176620076238</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4937743366645532</v>
+        <v>0.5003176620076238</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.494409660679801</v>
+        <v>0.5003176620076238</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4940738648436693</v>
+        <v>0.5003176620076238</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4940738648436693</v>
+        <v>0.5003176620076238</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.5009529860228716</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B156" t="n">
